--- a/backend/data/financials_by_company/0IK.F.xlsx
+++ b/backend/data/financials_by_company/0IK.F.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT5"/>
+  <dimension ref="A1:AU6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -649,201 +649,121 @@
           <t>Operating Revenue</t>
         </is>
       </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>Other Non Operating Income Expenses</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-817800</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="D2" t="n">
-        <v>32300000</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-2900000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-2900000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>10700000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>196300000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>29400000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>18700000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>13782200</v>
-      </c>
-      <c r="P2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>239000000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>17600000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>188699825</v>
+        <v>193415715</v>
       </c>
       <c r="T2" t="n">
-        <v>180514195</v>
+        <v>193415715</v>
       </c>
       <c r="U2" t="n">
-        <v>0.062</v>
+        <v>0.076783</v>
       </c>
       <c r="V2" t="n">
-        <v>0.0648</v>
-      </c>
-      <c r="W2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>11700000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4600000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>16300000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-2900000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>2900000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-1300000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2400000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>20500000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>42700000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>17900000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>7100000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>63200000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>196300000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>259500000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>259500000</v>
-      </c>
+        <v>0.076783</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.173</v>
+        <v>0.150388</v>
       </c>
       <c r="D3" t="n">
-        <v>45200000</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
+        <v>25456000</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="H3" t="n">
-        <v>6200000</v>
+        <v>5148000</v>
       </c>
       <c r="I3" t="n">
-        <v>199800000</v>
+        <v>145579000</v>
       </c>
       <c r="J3" t="n">
-        <v>45200000</v>
+        <v>25456000</v>
       </c>
       <c r="K3" t="n">
-        <v>39000000</v>
+        <v>20308000</v>
       </c>
       <c r="L3" t="n">
-        <v>600000</v>
+        <v>-171000</v>
       </c>
       <c r="M3" t="n">
-        <v>800000</v>
+        <v>220000</v>
       </c>
       <c r="N3" t="n">
-        <v>1400000</v>
+        <v>49000</v>
       </c>
       <c r="O3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="P3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="Q3" t="n">
-        <v>228200000</v>
+        <v>168624000</v>
       </c>
       <c r="R3" t="n">
-        <v>37600000</v>
+        <v>20068000</v>
       </c>
       <c r="S3" t="n">
         <v>193415715</v>
@@ -852,132 +772,131 @@
         <v>193415715</v>
       </c>
       <c r="U3" t="n">
-        <v>0.163379</v>
+        <v>0.08824</v>
       </c>
       <c r="V3" t="n">
-        <v>0.163379</v>
+        <v>0.08824</v>
       </c>
       <c r="W3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="X3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="AA3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="AB3" t="n">
-        <v>31600000</v>
+        <v>17067000</v>
       </c>
       <c r="AC3" t="n">
-        <v>6600000</v>
+        <v>3021000</v>
       </c>
       <c r="AD3" t="n">
-        <v>38200000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
+        <v>20088000</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>600000</v>
+        <v>-171000</v>
       </c>
       <c r="AH3" t="n">
-        <v>800000</v>
+        <v>220000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1400000</v>
+        <v>49000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>37600000</v>
+        <v>19235000</v>
       </c>
       <c r="AK3" t="n">
-        <v>28400000</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>3200000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>3200000</v>
-      </c>
+        <v>23045000</v>
+      </c>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
       <c r="AN3" t="n">
-        <v>10600000</v>
+        <v>9251000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6700000</v>
+        <v>13794000</v>
       </c>
       <c r="AP3" t="n">
-        <v>6700000</v>
+        <v>13794000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>66000000</v>
+        <v>42280000</v>
       </c>
       <c r="AR3" t="n">
-        <v>199800000</v>
+        <v>145579000</v>
       </c>
       <c r="AS3" t="n">
-        <v>265800000</v>
+        <v>187859000</v>
       </c>
       <c r="AT3" t="n">
-        <v>265800000</v>
-      </c>
+        <v>187859000</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.150388</v>
+        <v>0.173</v>
       </c>
       <c r="D4" t="n">
-        <v>25456000</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+        <v>45200000</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
       <c r="G4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="H4" t="n">
-        <v>5148000</v>
+        <v>6200000</v>
       </c>
       <c r="I4" t="n">
-        <v>145579000</v>
+        <v>199800000</v>
       </c>
       <c r="J4" t="n">
-        <v>25456000</v>
+        <v>45200000</v>
       </c>
       <c r="K4" t="n">
-        <v>20308000</v>
+        <v>39000000</v>
       </c>
       <c r="L4" t="n">
-        <v>-171000</v>
+        <v>600000</v>
       </c>
       <c r="M4" t="n">
-        <v>220000</v>
+        <v>800000</v>
       </c>
       <c r="N4" t="n">
-        <v>49000</v>
+        <v>1400000</v>
       </c>
       <c r="O4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="P4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="Q4" t="n">
-        <v>168624000</v>
+        <v>228200000</v>
       </c>
       <c r="R4" t="n">
-        <v>20068000</v>
+        <v>37600000</v>
       </c>
       <c r="S4" t="n">
         <v>193415715</v>
@@ -986,202 +905,355 @@
         <v>193415715</v>
       </c>
       <c r="U4" t="n">
-        <v>0.08824</v>
+        <v>0.163379</v>
       </c>
       <c r="V4" t="n">
-        <v>0.08824</v>
+        <v>0.163379</v>
       </c>
       <c r="W4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="X4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="AB4" t="n">
-        <v>17067000</v>
+        <v>31600000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3021000</v>
+        <v>6600000</v>
       </c>
       <c r="AD4" t="n">
-        <v>20088000</v>
-      </c>
-      <c r="AE4" t="inlineStr"/>
+        <v>38200000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="n">
-        <v>-171000</v>
+        <v>600000</v>
       </c>
       <c r="AH4" t="n">
-        <v>220000</v>
+        <v>800000</v>
       </c>
       <c r="AI4" t="n">
-        <v>49000</v>
+        <v>1400000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>19235000</v>
+        <v>37600000</v>
       </c>
       <c r="AK4" t="n">
-        <v>23045000</v>
-      </c>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
+        <v>28400000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>3200000</v>
+      </c>
       <c r="AN4" t="n">
-        <v>9251000</v>
+        <v>10600000</v>
       </c>
       <c r="AO4" t="n">
-        <v>13794000</v>
+        <v>6700000</v>
       </c>
       <c r="AP4" t="n">
-        <v>13794000</v>
+        <v>6700000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>42280000</v>
+        <v>66000000</v>
       </c>
       <c r="AR4" t="n">
-        <v>145579000</v>
+        <v>199800000</v>
       </c>
       <c r="AS4" t="n">
-        <v>187859000</v>
+        <v>265800000</v>
       </c>
       <c r="AT4" t="n">
-        <v>187859000</v>
-      </c>
+        <v>265800000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-818404.907975</v>
       </c>
       <c r="C5" t="n">
-        <v>0.19607</v>
+        <v>0.282209</v>
       </c>
       <c r="D5" t="n">
-        <v>22597000</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+        <v>32300000</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-2900000</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-2900000</v>
+      </c>
       <c r="G5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="H5" t="n">
-        <v>3809000</v>
+        <v>10700000</v>
       </c>
       <c r="I5" t="n">
-        <v>98670000</v>
+        <v>196300000</v>
       </c>
       <c r="J5" t="n">
-        <v>22597000</v>
+        <v>29400000</v>
       </c>
       <c r="K5" t="n">
-        <v>18788000</v>
+        <v>18700000</v>
       </c>
       <c r="L5" t="n">
-        <v>-315000</v>
+        <v>-1300000</v>
       </c>
       <c r="M5" t="n">
-        <v>315000</v>
+        <v>2400000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="O5" t="n">
-        <v>14851000</v>
+        <v>13781595.092025</v>
       </c>
       <c r="P5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>121550000</v>
+        <v>239000000</v>
       </c>
       <c r="R5" t="n">
-        <v>18765000</v>
+        <v>17600000</v>
       </c>
       <c r="S5" t="n">
-        <v>193415715</v>
+        <v>188699825</v>
       </c>
       <c r="T5" t="n">
-        <v>193415715</v>
+        <v>180514195</v>
       </c>
       <c r="U5" t="n">
-        <v>0.076783</v>
+        <v>0.062</v>
       </c>
       <c r="V5" t="n">
-        <v>0.076783</v>
+        <v>0.0648</v>
       </c>
       <c r="W5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="X5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="AA5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="AB5" t="n">
-        <v>14851000</v>
+        <v>11700000</v>
       </c>
       <c r="AC5" t="n">
-        <v>3622000</v>
+        <v>4600000</v>
       </c>
       <c r="AD5" t="n">
-        <v>18473000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
+        <v>16300000</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>-2900000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2900000</v>
+      </c>
       <c r="AG5" t="n">
-        <v>-315000</v>
+        <v>-1300000</v>
       </c>
       <c r="AH5" t="n">
-        <v>315000</v>
+        <v>2400000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19037000</v>
+        <v>20500000</v>
       </c>
       <c r="AK5" t="n">
-        <v>22880000</v>
-      </c>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+        <v>42700000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>4400000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>4400000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>11124000</v>
+        <v>17900000</v>
       </c>
       <c r="AO5" t="n">
-        <v>11793000</v>
+        <v>7100000</v>
       </c>
       <c r="AP5" t="n">
-        <v>11793000</v>
+        <v>7100000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>41917000</v>
+        <v>63200000</v>
       </c>
       <c r="AR5" t="n">
-        <v>98670000</v>
+        <v>196300000</v>
       </c>
       <c r="AS5" t="n">
-        <v>140587000</v>
+        <v>259500000</v>
       </c>
       <c r="AT5" t="n">
-        <v>140587000</v>
+        <v>259500000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.181132</v>
+      </c>
+      <c r="D6" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>245400000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39700000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>29200000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-1700000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>295500000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>28000000</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4800000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26500000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>-1700000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>27700000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>50100000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>77800000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>245400000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>323200000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>323200000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>300000</v>
       </c>
     </row>
   </sheetData>
@@ -1195,7 +1267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN5"/>
+  <dimension ref="A1:BO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1524,200 +1596,92 @@
           <t>Cash Financial</t>
         </is>
       </c>
+      <c r="BO1" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>155226</v>
-      </c>
-      <c r="C2" t="n">
-        <v>193260489</v>
-      </c>
-      <c r="D2" t="n">
-        <v>193415715</v>
-      </c>
-      <c r="E2" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>137200000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>210400000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>147100000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>137200000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>210400000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>210400000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>210400000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>210400000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>396400000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>32400000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>800000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>800000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>121000000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>22800000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>4700000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>10100000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>4800000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>98200000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>4400000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>700000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>84100000</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>83100000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>331400000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>86100000</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="n">
+        <v>80000</v>
+      </c>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>73200000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>73200000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>10600000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>-10700000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>21300000</v>
-      </c>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>8300000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>245300000</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="n">
+        <v>1779000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>156700000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>63800000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>92900000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>700000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>31000000</v>
-      </c>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
-      <c r="BJ2" t="n">
-        <v>31000000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>45800000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>45800000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>40000000</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>5800000</v>
-      </c>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
+      <c r="BN2" t="inlineStr"/>
+      <c r="BO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="inlineStr"/>
       <c r="C3" t="n">
@@ -1727,43 +1691,43 @@
         <v>185669950</v>
       </c>
       <c r="E3" t="n">
-        <v>7100000</v>
+        <v>1622000</v>
       </c>
       <c r="F3" t="n">
-        <v>100600000</v>
+        <v>71616000</v>
       </c>
       <c r="G3" t="n">
-        <v>159200000</v>
+        <v>107151000</v>
       </c>
       <c r="H3" t="n">
-        <v>109300000</v>
+        <v>79240000</v>
       </c>
       <c r="I3" t="n">
-        <v>100600000</v>
+        <v>71616000</v>
       </c>
       <c r="J3" t="n">
-        <v>7100000</v>
+        <v>1622000</v>
       </c>
       <c r="K3" t="n">
-        <v>159200000</v>
+        <v>107151000</v>
       </c>
       <c r="L3" t="n">
-        <v>159200000</v>
+        <v>107151000</v>
       </c>
       <c r="M3" t="n">
-        <v>159200000</v>
+        <v>107151000</v>
       </c>
       <c r="N3" t="n">
-        <v>159200000</v>
+        <v>107151000</v>
       </c>
       <c r="O3" t="n">
-        <v>1300000</v>
+        <v>1306000</v>
       </c>
       <c r="P3" t="n">
-        <v>92500000</v>
+        <v>60914000</v>
       </c>
       <c r="Q3" t="n">
-        <v>65400000</v>
+        <v>44931000</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1772,150 +1736,131 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>106100000</v>
+        <v>40251000</v>
       </c>
       <c r="U3" t="n">
-        <v>23200000</v>
+        <v>12732000</v>
       </c>
       <c r="V3" t="n">
-        <v>6425000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>4200000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>2200000</v>
-      </c>
+        <v>3700000</v>
+      </c>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>10200000</v>
+        <v>7673000</v>
       </c>
       <c r="Z3" t="n">
-        <v>5800000</v>
+        <v>1359000</v>
       </c>
       <c r="AA3" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>800000</v>
-      </c>
+        <v>1359000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>82900000</v>
+        <v>27519000</v>
       </c>
       <c r="AD3" t="n">
-        <v>8200000</v>
+        <v>1739000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1300000</v>
+        <v>263000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1300000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>400000</v>
-      </c>
+        <v>263000</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>64300000</v>
+        <v>21733000</v>
       </c>
       <c r="AI3" t="n">
-        <v>3382000</v>
+        <v>1815000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1900000</v>
+        <v>1914000</v>
       </c>
       <c r="AK3" t="n">
-        <v>62400000</v>
+        <v>18004000</v>
       </c>
       <c r="AL3" t="n">
-        <v>265300000</v>
+        <v>147402000</v>
       </c>
       <c r="AM3" t="n">
-        <v>73100000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>2698000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>2700000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
+        <v>40643000</v>
+      </c>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>58600000</v>
+        <v>35535000</v>
       </c>
       <c r="AR3" t="n">
-        <v>58600000</v>
+        <v>35535000</v>
       </c>
       <c r="AS3" t="n">
-        <v>11800000</v>
+        <v>5108000</v>
       </c>
       <c r="AT3" t="n">
-        <v>-7900000</v>
+        <v>-5732000</v>
       </c>
       <c r="AU3" t="n">
-        <v>19700000</v>
+        <v>10840000</v>
       </c>
       <c r="AV3" t="n">
-        <v>6849000</v>
+        <v>1487000</v>
       </c>
       <c r="AW3" t="n">
-        <v>11300000</v>
+        <v>9026000</v>
       </c>
       <c r="AX3" t="n">
-        <v>8400000</v>
+        <v>327000</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>192200000</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>-200000</v>
-      </c>
+        <v>106759000</v>
+      </c>
+      <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="n">
-        <v>2600000</v>
+        <v>3039000</v>
       </c>
       <c r="BC3" t="n">
-        <v>108100000</v>
+        <v>47889000</v>
       </c>
       <c r="BD3" t="n">
-        <v>40700000</v>
+        <v>11430000</v>
       </c>
       <c r="BE3" t="n">
-        <v>67400000</v>
+        <v>36459000</v>
       </c>
       <c r="BF3" t="n">
-        <v>700000</v>
+        <v>1840000</v>
       </c>
       <c r="BG3" t="n">
-        <v>8400000</v>
+        <v>0</v>
       </c>
       <c r="BH3" t="n">
-        <v>30200000</v>
+        <v>21148000</v>
       </c>
       <c r="BI3" t="n">
-        <v>-100000</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>30300000</v>
+        <v>21148000</v>
       </c>
       <c r="BK3" t="n">
-        <v>42200000</v>
+        <v>32843000</v>
       </c>
       <c r="BL3" t="n">
-        <v>42200000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>35700000</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>6500000</v>
-      </c>
+        <v>32843000</v>
+      </c>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="inlineStr"/>
       <c r="C4" t="n">
@@ -1925,43 +1870,43 @@
         <v>185669950</v>
       </c>
       <c r="E4" t="n">
-        <v>1622000</v>
+        <v>7100000</v>
       </c>
       <c r="F4" t="n">
-        <v>71616000</v>
+        <v>100600000</v>
       </c>
       <c r="G4" t="n">
-        <v>107151000</v>
+        <v>159200000</v>
       </c>
       <c r="H4" t="n">
-        <v>79240000</v>
+        <v>109300000</v>
       </c>
       <c r="I4" t="n">
-        <v>71616000</v>
+        <v>100600000</v>
       </c>
       <c r="J4" t="n">
-        <v>1622000</v>
+        <v>7100000</v>
       </c>
       <c r="K4" t="n">
-        <v>107151000</v>
+        <v>159200000</v>
       </c>
       <c r="L4" t="n">
-        <v>107151000</v>
+        <v>159200000</v>
       </c>
       <c r="M4" t="n">
-        <v>107151000</v>
+        <v>159200000</v>
       </c>
       <c r="N4" t="n">
-        <v>107151000</v>
+        <v>159200000</v>
       </c>
       <c r="O4" t="n">
-        <v>1306000</v>
+        <v>1300000</v>
       </c>
       <c r="P4" t="n">
-        <v>60914000</v>
+        <v>92500000</v>
       </c>
       <c r="Q4" t="n">
-        <v>44931000</v>
+        <v>65400000</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1970,302 +1915,527 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>40251000</v>
+        <v>106100000</v>
       </c>
       <c r="U4" t="n">
-        <v>12732000</v>
+        <v>23200000</v>
       </c>
       <c r="V4" t="n">
-        <v>3700000</v>
-      </c>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
+        <v>6425000</v>
+      </c>
+      <c r="W4" t="n">
+        <v>4200000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2200000</v>
+      </c>
       <c r="Y4" t="n">
-        <v>7673000</v>
+        <v>10200000</v>
       </c>
       <c r="Z4" t="n">
-        <v>1359000</v>
+        <v>5800000</v>
       </c>
       <c r="AA4" t="n">
-        <v>1359000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>5800000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>800000</v>
+      </c>
       <c r="AC4" t="n">
-        <v>27519000</v>
+        <v>82900000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1739000</v>
+        <v>8200000</v>
       </c>
       <c r="AE4" t="n">
-        <v>263000</v>
+        <v>1300000</v>
       </c>
       <c r="AF4" t="n">
-        <v>263000</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>1300000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>400000</v>
+      </c>
       <c r="AH4" t="n">
-        <v>21733000</v>
+        <v>64300000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1815000</v>
+        <v>3382000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1914000</v>
+        <v>1900000</v>
       </c>
       <c r="AK4" t="n">
-        <v>18004000</v>
+        <v>62400000</v>
       </c>
       <c r="AL4" t="n">
-        <v>147402000</v>
+        <v>265300000</v>
       </c>
       <c r="AM4" t="n">
-        <v>40643000</v>
-      </c>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+        <v>73100000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>2698000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>35535000</v>
+        <v>58600000</v>
       </c>
       <c r="AR4" t="n">
-        <v>35535000</v>
+        <v>58600000</v>
       </c>
       <c r="AS4" t="n">
-        <v>5108000</v>
+        <v>11800000</v>
       </c>
       <c r="AT4" t="n">
-        <v>-5732000</v>
+        <v>-7900000</v>
       </c>
       <c r="AU4" t="n">
-        <v>10840000</v>
+        <v>19700000</v>
       </c>
       <c r="AV4" t="n">
-        <v>1487000</v>
+        <v>6849000</v>
       </c>
       <c r="AW4" t="n">
-        <v>9026000</v>
+        <v>11300000</v>
       </c>
       <c r="AX4" t="n">
-        <v>327000</v>
+        <v>8400000</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>106759000</v>
-      </c>
-      <c r="BA4" t="inlineStr"/>
+        <v>192200000</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>-200000</v>
+      </c>
       <c r="BB4" t="n">
-        <v>3039000</v>
+        <v>2600000</v>
       </c>
       <c r="BC4" t="n">
-        <v>47889000</v>
+        <v>108100000</v>
       </c>
       <c r="BD4" t="n">
-        <v>11430000</v>
+        <v>40700000</v>
       </c>
       <c r="BE4" t="n">
-        <v>36459000</v>
+        <v>67400000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1840000</v>
+        <v>700000</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>8400000</v>
       </c>
       <c r="BH4" t="n">
-        <v>21148000</v>
+        <v>30200000</v>
       </c>
       <c r="BI4" t="n">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>21148000</v>
+        <v>30300000</v>
       </c>
       <c r="BK4" t="n">
-        <v>32843000</v>
+        <v>42200000</v>
       </c>
       <c r="BL4" t="n">
-        <v>32843000</v>
-      </c>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
+        <v>42200000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>35700000</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="BO4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
-      </c>
-      <c r="B5" t="inlineStr"/>
+        <v>45657</v>
+      </c>
+      <c r="B5" t="n">
+        <v>155226</v>
+      </c>
       <c r="C5" t="n">
-        <v>185669950</v>
+        <v>193260489</v>
       </c>
       <c r="D5" t="n">
-        <v>185669950</v>
+        <v>193415715</v>
       </c>
       <c r="E5" t="n">
-        <v>2116000</v>
+        <v>6200000</v>
       </c>
       <c r="F5" t="n">
-        <v>69714000</v>
+        <v>137200000</v>
       </c>
       <c r="G5" t="n">
-        <v>95521000</v>
+        <v>210400000</v>
       </c>
       <c r="H5" t="n">
-        <v>72641000</v>
+        <v>147100000</v>
       </c>
       <c r="I5" t="n">
-        <v>69714000</v>
+        <v>137200000</v>
       </c>
       <c r="J5" t="n">
-        <v>2116000</v>
+        <v>6200000</v>
       </c>
       <c r="K5" t="n">
-        <v>95521000</v>
+        <v>210400000</v>
       </c>
       <c r="L5" t="n">
-        <v>95521000</v>
+        <v>210400000</v>
       </c>
       <c r="M5" t="n">
-        <v>95521000</v>
+        <v>210400000</v>
       </c>
       <c r="N5" t="n">
-        <v>95521000</v>
+        <v>210400000</v>
       </c>
       <c r="O5" t="n">
-        <v>1717000</v>
+        <v>2700000</v>
       </c>
       <c r="P5" t="n">
-        <v>48892000</v>
+        <v>396400000</v>
       </c>
       <c r="Q5" t="n">
-        <v>44912000</v>
+        <v>32400000</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>800000</v>
       </c>
       <c r="T5" t="n">
-        <v>31263000</v>
+        <v>121000000</v>
       </c>
       <c r="U5" t="n">
-        <v>8165000</v>
+        <v>22800000</v>
       </c>
       <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>4700000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>6214000</v>
+        <v>10100000</v>
       </c>
       <c r="Z5" t="n">
-        <v>1951000</v>
+        <v>4800000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1951000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>4800000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1900000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>23098000</v>
+        <v>98200000</v>
       </c>
       <c r="AD5" t="n">
-        <v>2658000</v>
+        <v>4400000</v>
       </c>
       <c r="AE5" t="n">
-        <v>165000</v>
+        <v>1400000</v>
       </c>
       <c r="AF5" t="n">
-        <v>165000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>1400000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>700000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>16933000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>80000</v>
-      </c>
+        <v>84100000</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>1676000</v>
+        <v>1000000</v>
       </c>
       <c r="AK5" t="n">
-        <v>15177000</v>
+        <v>83100000</v>
       </c>
       <c r="AL5" t="n">
-        <v>126784000</v>
+        <v>331400000</v>
       </c>
       <c r="AM5" t="n">
-        <v>31045000</v>
+        <v>86100000</v>
       </c>
       <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
+      <c r="AO5" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>300000</v>
+      </c>
       <c r="AQ5" t="n">
-        <v>25807000</v>
+        <v>73200000</v>
       </c>
       <c r="AR5" t="n">
-        <v>25807000</v>
+        <v>73200000</v>
       </c>
       <c r="AS5" t="n">
-        <v>5238000</v>
+        <v>10600000</v>
       </c>
       <c r="AT5" t="n">
-        <v>-3755000</v>
+        <v>-10700000</v>
       </c>
       <c r="AU5" t="n">
-        <v>8993000</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>1779000</v>
-      </c>
+        <v>21300000</v>
+      </c>
+      <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="n">
-        <v>6887000</v>
+        <v>13000000</v>
       </c>
       <c r="AX5" t="n">
-        <v>327000</v>
+        <v>8300000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>95739000</v>
+        <v>245300000</v>
       </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="n">
-        <v>4588000</v>
+        <v>3600000</v>
       </c>
       <c r="BC5" t="n">
-        <v>40576000</v>
+        <v>156700000</v>
       </c>
       <c r="BD5" t="n">
-        <v>14894000</v>
+        <v>63800000</v>
       </c>
       <c r="BE5" t="n">
-        <v>25682000</v>
+        <v>92900000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1058000</v>
+        <v>700000</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>7500000</v>
       </c>
       <c r="BH5" t="n">
-        <v>15088000</v>
+        <v>31000000</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>15088000</v>
+        <v>31000000</v>
       </c>
       <c r="BK5" t="n">
-        <v>34429000</v>
+        <v>45800000</v>
       </c>
       <c r="BL5" t="n">
-        <v>34429000</v>
-      </c>
-      <c r="BM5" t="inlineStr"/>
-      <c r="BN5" t="inlineStr"/>
+        <v>45800000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>40000000</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>5800000</v>
+      </c>
+      <c r="BO5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>155226</v>
+      </c>
+      <c r="C6" t="n">
+        <v>193426923</v>
+      </c>
+      <c r="D6" t="n">
+        <v>193582149</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>157600000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>240800000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>172800000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>157600000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8900000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>240800000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>240800000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>240800000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>240800000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>10600000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>417300000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>34000000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>90800000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>29100000</v>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>6900000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>13200000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8100000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>900000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>61700000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>300000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>47700000</v>
+      </c>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>46500000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>331600000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>97100000</v>
+      </c>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>83200000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>83200000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>12500000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>-13100000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>25600000</v>
+      </c>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="n">
+        <v>14700000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10900000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>234500000</v>
+      </c>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>145300000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>31200000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>114100000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>800000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>52600000</v>
+      </c>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="n">
+        <v>52600000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>28300000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>28100000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>17000000</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>11100000</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>200000</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2278,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AS5"/>
+  <dimension ref="A1:AS6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2505,119 +2675,77 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>-26300000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="n">
-        <v>40800000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-23100000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>45800000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>42200000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>29800000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>-15154000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>15190000</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="n">
-        <v>-1200000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="n">
-        <v>40800000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>40800000</v>
-      </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="n">
-        <v>-23100000</v>
-      </c>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>-4041000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>36000</v>
+      </c>
+      <c r="S2" t="n">
+        <v>-15154000</v>
+      </c>
+      <c r="T2" t="n">
+        <v>15190000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
-      <c r="W2" t="n">
-        <v>-20900000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>-20900000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-2200000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="n">
-        <v>-3200000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>-4200000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1100000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>-34300000</v>
-      </c>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>-4584000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="n">
-        <v>13000000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-51100000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>700000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>10700000</v>
-      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="n">
-        <v>10700000</v>
-      </c>
+      <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>17600000</v>
-      </c>
+      <c r="AQ2" t="n">
+        <v>-31000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-2000000</v>
+        <v>3594000</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -2626,38 +2754,40 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>15100000</v>
+        <v>19000</v>
       </c>
       <c r="F3" t="n">
-        <v>-23100000</v>
+        <v>-10745000</v>
       </c>
       <c r="G3" t="n">
-        <v>42200000</v>
+        <v>32843000</v>
       </c>
       <c r="H3" t="n">
-        <v>32800000</v>
+        <v>34429000</v>
       </c>
       <c r="I3" t="n">
-        <v>100000</v>
+        <v>319000</v>
       </c>
       <c r="J3" t="n">
-        <v>9300000</v>
+        <v>-1905000</v>
       </c>
       <c r="K3" t="n">
-        <v>14000000</v>
+        <v>-5499000</v>
       </c>
       <c r="L3" t="n">
-        <v>1443000</v>
+        <v>49000</v>
       </c>
       <c r="M3" t="n">
-        <v>-800000</v>
-      </c>
-      <c r="N3" t="inlineStr"/>
+        <v>-220000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-5045000</v>
+      </c>
       <c r="O3" t="n">
-        <v>15100000</v>
+        <v>19000</v>
       </c>
       <c r="P3" t="n">
-        <v>15100000</v>
+        <v>19000</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -2672,87 +2802,77 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>-25800000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-2700000</v>
-      </c>
+        <v>-10745000</v>
+      </c>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-19200000</v>
+        <v>-1589000</v>
       </c>
       <c r="X3" t="n">
-        <v>-19200000</v>
+        <v>-1589000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-3900000</v>
+        <v>-2139000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-3900000</v>
+        <v>-2139000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-14410000</v>
+        <v>-7017000</v>
       </c>
       <c r="AB3" t="n">
-        <v>21100000</v>
+        <v>14339000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-4700000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1400000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>-19300000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-2698000</v>
-      </c>
+        <v>-9655000</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="n">
-        <v>54100000</v>
+        <v>2951000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-60200000</v>
+        <v>-7313000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-13600000</v>
+        <v>-5293000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>200000</v>
+        <v>-20000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>-411000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-500000</v>
+        <v>-490000</v>
       </c>
       <c r="AM3" t="n">
-        <v>6200000</v>
+        <v>5148000</v>
       </c>
       <c r="AN3" t="n">
-        <v>3017000</v>
+        <v>2879000</v>
       </c>
       <c r="AO3" t="n">
-        <v>6200000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>237000</v>
-      </c>
+        <v>2269000</v>
+      </c>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="n">
-        <v>-140000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>200000</v>
-      </c>
+        <v>-321000</v>
+      </c>
+      <c r="AR3" t="inlineStr"/>
       <c r="AS3" t="n">
-        <v>37600000</v>
+        <v>20088000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>3594000</v>
+        <v>-2000000</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -2761,40 +2881,38 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>19000</v>
+        <v>15100000</v>
       </c>
       <c r="F4" t="n">
-        <v>-10745000</v>
+        <v>-23100000</v>
       </c>
       <c r="G4" t="n">
-        <v>32843000</v>
+        <v>42200000</v>
       </c>
       <c r="H4" t="n">
-        <v>34429000</v>
+        <v>32800000</v>
       </c>
       <c r="I4" t="n">
-        <v>319000</v>
+        <v>100000</v>
       </c>
       <c r="J4" t="n">
-        <v>-1905000</v>
+        <v>9300000</v>
       </c>
       <c r="K4" t="n">
-        <v>-5499000</v>
+        <v>14000000</v>
       </c>
       <c r="L4" t="n">
-        <v>49000</v>
+        <v>1443000</v>
       </c>
       <c r="M4" t="n">
-        <v>-220000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-5045000</v>
-      </c>
+        <v>-800000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="n">
-        <v>19000</v>
+        <v>15100000</v>
       </c>
       <c r="P4" t="n">
-        <v>19000</v>
+        <v>15100000</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -2809,194 +2927,305 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-10745000</v>
-      </c>
-      <c r="V4" t="inlineStr"/>
+        <v>-25800000</v>
+      </c>
+      <c r="V4" t="n">
+        <v>-2700000</v>
+      </c>
       <c r="W4" t="n">
-        <v>-1589000</v>
+        <v>-19200000</v>
       </c>
       <c r="X4" t="n">
-        <v>-1589000</v>
+        <v>-19200000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-2139000</v>
+        <v>-3900000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-2139000</v>
+        <v>-3900000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-7017000</v>
+        <v>-14410000</v>
       </c>
       <c r="AB4" t="n">
-        <v>14339000</v>
+        <v>21100000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="inlineStr"/>
+        <v>-4700000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1400000</v>
+      </c>
       <c r="AE4" t="n">
-        <v>-9655000</v>
-      </c>
-      <c r="AF4" t="inlineStr"/>
+        <v>-19300000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-2698000</v>
+      </c>
       <c r="AG4" t="n">
-        <v>2951000</v>
+        <v>54100000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-7313000</v>
+        <v>-60200000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-5293000</v>
+        <v>-13600000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-20000</v>
+        <v>200000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-411000</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>-490000</v>
+        <v>-500000</v>
       </c>
       <c r="AM4" t="n">
-        <v>5148000</v>
+        <v>6200000</v>
       </c>
       <c r="AN4" t="n">
-        <v>2879000</v>
+        <v>3017000</v>
       </c>
       <c r="AO4" t="n">
-        <v>2269000</v>
-      </c>
-      <c r="AP4" t="inlineStr"/>
+        <v>6200000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>237000</v>
+      </c>
       <c r="AQ4" t="n">
-        <v>-321000</v>
-      </c>
-      <c r="AR4" t="inlineStr"/>
+        <v>-140000</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>200000</v>
+      </c>
       <c r="AS4" t="n">
-        <v>20088000</v>
+        <v>37600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-6870000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-15154000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>15190000</v>
-      </c>
+        <v>-26300000</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>44894000</v>
+        <v>40800000</v>
       </c>
       <c r="F5" t="n">
-        <v>-7380000</v>
+        <v>-23100000</v>
       </c>
       <c r="G5" t="n">
-        <v>34429000</v>
+        <v>45800000</v>
       </c>
       <c r="H5" t="n">
-        <v>1055000</v>
+        <v>42200000</v>
       </c>
       <c r="I5" t="n">
-        <v>-5000</v>
+        <v>100000</v>
       </c>
       <c r="J5" t="n">
-        <v>33379000</v>
+        <v>3500000</v>
       </c>
       <c r="K5" t="n">
-        <v>40249000</v>
+        <v>29800000</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>-315000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-4041000</v>
-      </c>
+        <v>-1200000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>44894000</v>
+        <v>40800000</v>
       </c>
       <c r="P5" t="n">
-        <v>44894000</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>36000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>36000</v>
-      </c>
-      <c r="S5" t="n">
-        <v>-15154000</v>
-      </c>
-      <c r="T5" t="n">
-        <v>15190000</v>
-      </c>
+        <v>40800000</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>-7380000</v>
+        <v>-23100000</v>
       </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-20900000</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-20900000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-2796000</v>
+        <v>-2200000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2796000</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>-4584000</v>
-      </c>
+        <v>-2200000</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
       <c r="AB5" t="n">
-        <v>510000</v>
+        <v>-3200000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>-4200000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1100000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-23237000</v>
+        <v>-34300000</v>
       </c>
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="n">
-        <v>4902000</v>
+        <v>13000000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-21660000</v>
+        <v>-51100000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-6479000</v>
+        <v>3500000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>292000</v>
+        <v>700000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1204000</v>
+        <v>6000000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-800000</v>
       </c>
       <c r="AM5" t="n">
-        <v>3809000</v>
+        <v>10700000</v>
       </c>
       <c r="AN5" t="n">
-        <v>2113000</v>
+        <v>6300000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1696000</v>
+        <v>4400000</v>
       </c>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="n">
-        <v>-31000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
       <c r="AS5" t="n">
-        <v>18473000</v>
+        <v>17600000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-12100000</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-18300000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>28100000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>45800000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-17800000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-5800000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-3000000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-1400000</v>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>200000</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="n">
+        <v>-18200000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-16500000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-16500000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-1800000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-1800000</v>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="n">
+        <v>6200000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5300000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>600000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>-45800000</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="n">
+        <v>-34900000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-21900000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>400000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>7900000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>-500000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>6800000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>3700000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>-200000</v>
+      </c>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="n">
+        <v>28000000</v>
       </c>
     </row>
   </sheetData>
@@ -3010,7 +3239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EO2"/>
+  <dimension ref="A1:EP2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3186,555 +3415,560 @@
       </c>
       <c r="AI1" t="inlineStr">
         <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
           <t>trailingPE</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>volume</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>regularMarketVolume</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>averageVolume</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>averageVolume10days</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>averageDailyVolume10Day</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>bid</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>ask</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>marketCap</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>nonDilutedMarketCap</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLow</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHigh</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>allTimeHigh</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>allTimeLow</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>priceToSalesTrailing12Months</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>fiftyDayAverage</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverage</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendRate</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>trailingAnnualDividendYield</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>tradeable</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>enterpriseValue</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>profitMargins</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>floatShares</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>sharesOutstanding</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>heldPercentInsiders</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>heldPercentInstitutions</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>impliedSharesOutstanding</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>bookValue</t>
         </is>
       </c>
-      <c r="BL1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="BM1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>lastFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BN1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>nextFiscalYearEnd</t>
         </is>
       </c>
-      <c r="BO1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>mostRecentQuarter</t>
         </is>
       </c>
-      <c r="BP1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>earningsQuarterlyGrowth</t>
         </is>
       </c>
-      <c r="BQ1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>netIncomeToCommon</t>
         </is>
       </c>
-      <c r="BR1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>trailingEps</t>
         </is>
       </c>
-      <c r="BS1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>enterpriseToRevenue</t>
         </is>
       </c>
-      <c r="BT1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>enterpriseToEbitda</t>
         </is>
       </c>
-      <c r="BU1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>52WeekChange</t>
         </is>
       </c>
-      <c r="BV1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>SandP52WeekChange</t>
         </is>
       </c>
-      <c r="BW1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>quoteType</t>
         </is>
       </c>
-      <c r="BX1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>currentPrice</t>
         </is>
       </c>
-      <c r="BY1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>recommendationKey</t>
         </is>
       </c>
-      <c r="BZ1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>totalCash</t>
         </is>
       </c>
-      <c r="CA1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>totalCashPerShare</t>
         </is>
       </c>
-      <c r="CB1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>ebitda</t>
         </is>
       </c>
-      <c r="CC1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>totalDebt</t>
         </is>
       </c>
-      <c r="CD1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>quickRatio</t>
         </is>
       </c>
-      <c r="CE1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>currentRatio</t>
         </is>
       </c>
-      <c r="CF1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>totalRevenue</t>
         </is>
       </c>
-      <c r="CG1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>debtToEquity</t>
         </is>
       </c>
-      <c r="CH1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>revenuePerShare</t>
         </is>
       </c>
-      <c r="CI1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>returnOnAssets</t>
         </is>
       </c>
-      <c r="CJ1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>returnOnEquity</t>
         </is>
       </c>
-      <c r="CK1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>grossProfits</t>
         </is>
       </c>
-      <c r="CL1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>freeCashflow</t>
         </is>
       </c>
-      <c r="CM1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>operatingCashflow</t>
         </is>
       </c>
-      <c r="CN1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>earningsGrowth</t>
         </is>
       </c>
-      <c r="CO1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>revenueGrowth</t>
         </is>
       </c>
-      <c r="CP1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>grossMargins</t>
         </is>
       </c>
-      <c r="CQ1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>ebitdaMargins</t>
         </is>
       </c>
-      <c r="CR1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>operatingMargins</t>
         </is>
       </c>
-      <c r="CS1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>financialCurrency</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>language</t>
         </is>
       </c>
-      <c r="CV1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="CW1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>typeDisp</t>
         </is>
       </c>
-      <c r="CX1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>quoteSourceName</t>
         </is>
       </c>
-      <c r="CY1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>triggerable</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>customPriceAlertConfidence</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>prevName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>nameChangeDate</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
         <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="EL1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -3811,7 +4045,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Eben Christopher Upton CBE', 'age': 47, 'title': 'Founder, CEO &amp; Director', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 975733, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Richard David Boult', 'age': 60, 'title': 'CFO, Secretary &amp; Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 759801, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tim  Mamtora', 'title': 'Chief Operating Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Carol  Copland', 'age': 50, 'title': 'General Counsel &amp; Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Helen  Lynn', 'title': 'Director of Communications', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mike  Buffham', 'age': 63, 'title': 'Chief Commercial Officer', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Gordon Scott Hollingworth', 'age': 54, 'title': 'Chief Technical Officer of Software', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James Robert Adams', 'age': 45, 'title': 'Chief Technical Officer of Hardware', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Eben Christopher Upton CBE', 'age': 47, 'title': 'Founder, CEO &amp; Director', 'yearBorn': 1978, 'fiscalYear': 2025, 'totalPay': 978064, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Richard David Boult', 'age': 60, 'title': 'CFO, Secretary &amp; Director', 'yearBorn': 1965, 'fiscalYear': 2025, 'totalPay': 761617, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tim  Mamtora', 'title': 'Chief Operating Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Carol  Copland', 'age': 50, 'title': 'General Counsel &amp; Company Secretary', 'yearBorn': 1975, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Helen  Lynn', 'title': 'Director of Communications', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Mike  Buffham', 'age': 63, 'title': 'Chief Commercial Officer', 'yearBorn': 1962, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Gordon Scott Hollingworth', 'age': 54, 'title': 'Chief Technical Officer of Software', 'yearBorn': 1971, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. James Robert Adams', 'age': 45, 'title': 'Chief Technical Officer of Hardware', 'yearBorn': 1980, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3830,7 +4064,7 @@
         <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="n">
         <v>1767139200</v>
@@ -3847,409 +4081,412 @@
         <v>2</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.279999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.404999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.404999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>10.36</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>9.279999999999999</v>
+        <v>10.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>9.404999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.404999999999999</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.36</v>
+        <v>9.994999999999999</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>258.75003</v>
+        <v>0.502</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2020</v>
+        <v>99.95</v>
       </c>
       <c r="AK2" t="n">
-        <v>2020</v>
+        <v>102</v>
       </c>
       <c r="AL2" t="n">
-        <v>577</v>
+        <v>102</v>
       </c>
       <c r="AM2" t="n">
-        <v>663</v>
+        <v>604</v>
       </c>
       <c r="AN2" t="n">
-        <v>663</v>
+        <v>572</v>
       </c>
       <c r="AO2" t="n">
-        <v>10.33</v>
+        <v>572</v>
       </c>
       <c r="AP2" t="n">
-        <v>10.5</v>
+        <v>10.02</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2003322240</v>
+        <v>10.43</v>
       </c>
       <c r="AR2" t="n">
-        <v>1817083340</v>
+        <v>1934609152</v>
       </c>
       <c r="AS2" t="n">
+        <v>1977774468</v>
+      </c>
+      <c r="AT2" t="n">
         <v>3.01</v>
       </c>
-      <c r="AT2" t="n">
-        <v>10.36</v>
-      </c>
       <c r="AU2" t="n">
-        <v>9.715</v>
+        <v>12.72</v>
       </c>
       <c r="AV2" t="n">
+        <v>12.72</v>
+      </c>
+      <c r="AW2" t="n">
         <v>3.01</v>
       </c>
-      <c r="AW2" t="n">
-        <v>6.198398</v>
-      </c>
       <c r="AX2" t="n">
-        <v>6.8294</v>
+        <v>5.9857955</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.64785</v>
+        <v>8.3209</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>5.002375</v>
       </c>
       <c r="BA2" t="n">
         <v>0</v>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="BC2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>1984375296</v>
+      <c r="BD2" t="b">
+        <v>0</v>
       </c>
       <c r="BE2" t="n">
+        <v>1877905024</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.067140006</v>
       </c>
-      <c r="BF2" t="n">
-        <v>77924558</v>
-      </c>
       <c r="BG2" t="n">
+        <v>78116205</v>
+      </c>
+      <c r="BH2" t="n">
         <v>193557701</v>
       </c>
-      <c r="BH2" t="n">
-        <v>0.6188399999999999</v>
-      </c>
       <c r="BI2" t="n">
-        <v>0.22856002</v>
+        <v>0.61755</v>
       </c>
       <c r="BJ2" t="n">
+        <v>0.22669001</v>
+      </c>
+      <c r="BK2" t="n">
         <v>193557701</v>
       </c>
-      <c r="BK2" t="n">
-        <v>1.0679945</v>
-      </c>
       <c r="BL2" t="n">
-        <v>9.691062000000001</v>
+        <v>1.0733391</v>
       </c>
       <c r="BM2" t="n">
+        <v>9.312061</v>
+      </c>
+      <c r="BN2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BO2" t="n">
         <v>1798675200</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BP2" t="n">
         <v>1767139200</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BQ2" t="n">
         <v>2.976</v>
       </c>
-      <c r="BQ2" t="n">
+      <c r="BR2" t="n">
         <v>21700000</v>
       </c>
-      <c r="BR2" t="n">
-        <v>0.04</v>
-      </c>
       <c r="BS2" t="n">
-        <v>6.14</v>
+        <v>0.1</v>
       </c>
       <c r="BT2" t="n">
-        <v>54.218</v>
+        <v>5.81</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.73134327</v>
+        <v>51.309</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27294624</v>
-      </c>
-      <c r="BW2" t="inlineStr">
+        <v>0.8874539</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>0.2568333</v>
+      </c>
+      <c r="BX2" t="inlineStr">
         <is>
           <t>EQUITY</t>
         </is>
       </c>
-      <c r="BX2" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BY2" t="n">
+        <v>9.994999999999999</v>
+      </c>
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="BZ2" t="n">
+      <c r="CA2" t="n">
         <v>28100000</v>
       </c>
-      <c r="CA2" t="n">
+      <c r="CB2" t="n">
         <v>0.145</v>
       </c>
-      <c r="CB2" t="n">
+      <c r="CC2" t="n">
         <v>36600000</v>
       </c>
-      <c r="CC2" t="n">
+      <c r="CD2" t="n">
         <v>8900000</v>
       </c>
-      <c r="CD2" t="n">
+      <c r="CE2" t="n">
         <v>1.37</v>
       </c>
-      <c r="CE2" t="n">
+      <c r="CF2" t="n">
         <v>3.801</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CG2" t="n">
         <v>323200000</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CH2" t="n">
         <v>3.696</v>
       </c>
-      <c r="CH2" t="n">
+      <c r="CI2" t="n">
         <v>1.672</v>
       </c>
-      <c r="CI2" t="n">
+      <c r="CJ2" t="n">
         <v>0.05222</v>
       </c>
-      <c r="CJ2" t="n">
+      <c r="CK2" t="n">
         <v>0.09619000599999999</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CL2" t="n">
         <v>77800000</v>
       </c>
-      <c r="CL2" t="n">
+      <c r="CM2" t="n">
         <v>-25462500</v>
       </c>
-      <c r="CM2" t="n">
+      <c r="CN2" t="n">
         <v>6200000</v>
       </c>
-      <c r="CN2" t="n">
+      <c r="CO2" t="n">
         <v>3.097</v>
       </c>
-      <c r="CO2" t="n">
+      <c r="CP2" t="n">
         <v>0.625</v>
       </c>
-      <c r="CP2" t="n">
+      <c r="CQ2" t="n">
         <v>0.24072</v>
       </c>
-      <c r="CQ2" t="n">
+      <c r="CR2" t="n">
         <v>0.11324</v>
       </c>
-      <c r="CR2" t="n">
+      <c r="CS2" t="n">
         <v>0.104949996</v>
       </c>
-      <c r="CS2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="CT2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>0IK.F</t>
         </is>
       </c>
-      <c r="CU2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>en-US</t>
         </is>
       </c>
-      <c r="CV2" t="inlineStr">
+      <c r="CW2" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="CW2" t="inlineStr">
+      <c r="CX2" t="inlineStr">
         <is>
           <t>Equity</t>
         </is>
       </c>
-      <c r="CX2" t="inlineStr">
+      <c r="CY2" t="inlineStr">
         <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="CY2" t="b">
-        <v>0</v>
-      </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="CZ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DA2" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>0.04</v>
-      </c>
       <c r="DB2" t="n">
-        <v>3.5206003</v>
+        <v>-2.2971618</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.5155065</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>5.7021503</v>
+        <v>9.994999999999999</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Raspberry Pi Holdings PLC     R</t>
+        </is>
       </c>
       <c r="DE2" t="n">
-        <v>1.2268361</v>
-      </c>
-      <c r="DF2" t="n">
+        <v>-0.23499966</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>9.87 - 9.995</t>
+        </is>
+      </c>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>Frankfurt</t>
+        </is>
+      </c>
+      <c r="DH2" t="n">
+        <v>604</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>6.9849997</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>2.320598</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>3.01 - 12.72</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>-2.7250004</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.21422958</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>88.74539</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1743591540</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>1743591540</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>1743582600</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1743582600</v>
+      </c>
+      <c r="DS2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1.6740999</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0.20119217</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>4.9926248</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.99805087</v>
+      </c>
+      <c r="DY2" t="n">
         <v>15</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DZ2" t="n">
         <v>15</v>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Raspberry Pi Ltd</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="DJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>577</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>2.4385383</v>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>3.01 - 10.36</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.009999275</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-0.00096518104</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>73.13432</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>1743591540</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>1743591540</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>1743582600</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1743582600</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>11.53018</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Raspberry Pi Holdings PLC     R</t>
-        </is>
-      </c>
       <c r="EB2" t="inlineStr">
         <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="EC2" t="b">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>finmb_271153436</t>
+        </is>
+      </c>
+      <c r="EG2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="EJ2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="EK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EL2" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EC2" t="n">
-        <v>1780415289</v>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>finmb_271153436</t>
-        </is>
-      </c>
-      <c r="EF2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EL2" t="n">
+      <c r="EM2" t="n">
+        <v>1781875502</v>
+      </c>
+      <c r="EN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="n">
         <v>1718604000000</v>
       </c>
-      <c r="EM2" t="n">
-        <v>1.0700006</v>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>9.405 - 10.36</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr"/>
+      <c r="EP2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
